--- a/Assets/Excel/StorageBag.xlsx
+++ b/Assets/Excel/StorageBag.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="15870" windowHeight="9825"/>
   </bookViews>
   <sheets>
     <sheet name="StotageBagData" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -40,12 +40,24 @@
     <t>capacity</t>
   </si>
   <si>
+    <t>unlockStr</t>
+  </si>
+  <si>
+    <t>lockType</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>UnlockType</t>
+  </si>
+  <si>
     <t>标识ID</t>
   </si>
   <si>
@@ -55,22 +67,46 @@
     <t>储物袋增加的容量</t>
   </si>
   <si>
+    <t>解锁条件</t>
+  </si>
+  <si>
+    <t>解锁类型</t>
+  </si>
+  <si>
+    <t>条件值</t>
+  </si>
+  <si>
     <t>云纹袋</t>
   </si>
   <si>
     <t>灵叶锦囊</t>
   </si>
   <si>
+    <t>账号等级到达5级</t>
+  </si>
+  <si>
     <t>云月戒</t>
   </si>
   <si>
+    <t>天赋等级到达20级</t>
+  </si>
+  <si>
     <t>芝云玉</t>
   </si>
   <si>
+    <t>累积转动仙运转盘50次</t>
+  </si>
+  <si>
     <t>缠花袋</t>
   </si>
   <si>
+    <t>升级令最高等级达到10级</t>
+  </si>
+  <si>
     <t>墨玉戒</t>
+  </si>
+  <si>
+    <t>购买套装获得</t>
   </si>
 </sst>
 </file>
@@ -1013,15 +1049,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="17.75" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1031,93 +1069,171 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
       </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
       </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
+      </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
         <v>8</v>
       </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
       </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/StorageBag.xlsx
+++ b/Assets/Excel/StorageBag.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15870" windowHeight="9825"/>
+    <workbookView windowWidth="12510" windowHeight="10275"/>
   </bookViews>
   <sheets>
     <sheet name="StotageBagData" sheetId="1" r:id="rId1"/>
@@ -1153,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">

--- a/Assets/Excel/StorageBag.xlsx
+++ b/Assets/Excel/StorageBag.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12510" windowHeight="10275"/>
+    <workbookView windowWidth="15030" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="StotageBagData" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -49,6 +49,12 @@
     <t>value</t>
   </si>
   <si>
+    <t>attachmentName</t>
+  </si>
+  <si>
+    <t>slotName</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -76,37 +82,64 @@
     <t>条件值</t>
   </si>
   <si>
+    <t>插槽图片字段</t>
+  </si>
+  <si>
+    <t>插槽字段</t>
+  </si>
+  <si>
     <t>云纹袋</t>
   </si>
   <si>
+    <t>袋/7</t>
+  </si>
+  <si>
+    <t>dai</t>
+  </si>
+  <si>
     <t>灵叶锦囊</t>
   </si>
   <si>
     <t>账号等级到达5级</t>
   </si>
   <si>
+    <t>袋/8</t>
+  </si>
+  <si>
     <t>云月戒</t>
   </si>
   <si>
     <t>天赋等级到达20级</t>
   </si>
   <si>
+    <t>袋/9</t>
+  </si>
+  <si>
+    <t>墨玉戒</t>
+  </si>
+  <si>
+    <t>累积转动仙运转盘50次</t>
+  </si>
+  <si>
+    <t>袋/12</t>
+  </si>
+  <si>
+    <t>缠花袋</t>
+  </si>
+  <si>
+    <t>升级令最高等级达到10级</t>
+  </si>
+  <si>
+    <t>袋/11</t>
+  </si>
+  <si>
     <t>芝云玉</t>
   </si>
   <si>
-    <t>累积转动仙运转盘50次</t>
-  </si>
-  <si>
-    <t>缠花袋</t>
-  </si>
-  <si>
-    <t>升级令最高等级达到10级</t>
-  </si>
-  <si>
-    <t>墨玉戒</t>
-  </si>
-  <si>
     <t>购买套装获得</t>
+  </si>
+  <si>
+    <t>袋/10</t>
   </si>
 </sst>
 </file>
@@ -1049,17 +1082,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="17.75" customWidth="1"/>
     <col min="4" max="4" width="21.875" customWidth="1"/>
     <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="7" max="7" width="20.875" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,53 +1113,71 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>6</v>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1135,19 +1188,25 @@
       <c r="F4">
         <v>0</v>
       </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1155,19 +1214,25 @@
       <c r="F5">
         <v>5</v>
       </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1175,19 +1240,25 @@
       <c r="F6">
         <v>20</v>
       </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1195,19 +1266,25 @@
       <c r="F7">
         <v>50</v>
       </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1215,25 +1292,37 @@
       <c r="F8">
         <v>10</v>
       </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9">
         <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
